--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -555,22 +555,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -587,22 +590,25 @@
         <v>43</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>97.67</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>2.33</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -651,22 +657,25 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -683,22 +692,25 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2109,22 +2121,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2141,22 +2156,25 @@
         <v>43</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>97.67</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>2.33</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2205,22 +2223,25 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2237,22 +2258,25 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -625,22 +625,25 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>92.31</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>7.69</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.7</v>
       </c>
       <c r="J4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -727,22 +730,25 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>7.32</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -969,25 +975,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>63.33</v>
+        <v>93.33</v>
       </c>
       <c r="H14" s="1">
-        <v>36.67</v>
+        <v>6.67</v>
       </c>
       <c r="I14" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1004,25 +1010,25 @@
         <v>31</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1">
-        <v>58.06</v>
+        <v>61.29</v>
       </c>
       <c r="H15" s="1">
-        <v>41.94</v>
+        <v>38.71</v>
       </c>
       <c r="I15" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1054,10 +1060,10 @@
         <v>7.3</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1109,22 +1115,25 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>10.71</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.7</v>
       </c>
       <c r="J18">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1141,25 +1150,25 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>35.71</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>35.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2191,22 +2200,25 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>92.31</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>7.69</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.7</v>
       </c>
       <c r="J4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2293,22 +2305,25 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>7.32</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2535,25 +2550,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>63.33</v>
+        <v>93.33</v>
       </c>
       <c r="H14" s="1">
-        <v>36.67</v>
+        <v>6.67</v>
       </c>
       <c r="I14" s="2">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2570,25 +2585,25 @@
         <v>31</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1">
-        <v>58.06</v>
+        <v>61.29</v>
       </c>
       <c r="H15" s="1">
-        <v>41.94</v>
+        <v>38.71</v>
       </c>
       <c r="I15" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2617,13 +2632,13 @@
         <v>9.09</v>
       </c>
       <c r="I16" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2675,22 +2690,25 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>10.71</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.7</v>
       </c>
       <c r="J18">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2707,25 +2725,25 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>35.71</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>35.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -1290,22 +1290,25 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F23">
+        <v>21</v>
+      </c>
+      <c r="G23" s="1">
         <v>30</v>
       </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>70</v>
+      </c>
+      <c r="I23" s="2">
+        <v>4.8</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2865,22 +2868,25 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F23">
+        <v>21</v>
+      </c>
+      <c r="G23" s="1">
         <v>30</v>
       </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>70</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5.5</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -1042,28 +1042,28 @@
         <v>38</v>
       </c>
       <c r="D16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>30</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>9.09</v>
+        <v>11.76</v>
       </c>
       <c r="I16" s="2">
         <v>7.3</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1112,28 +1112,28 @@
         <v>38</v>
       </c>
       <c r="D18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18">
         <v>25</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>10.71</v>
+        <v>13.79</v>
       </c>
       <c r="I18" s="2">
         <v>7.7</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1822,13 +1822,13 @@
         <v>38</v>
       </c>
       <c r="D16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1837,7 +1837,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -1886,13 +1886,13 @@
         <v>38</v>
       </c>
       <c r="D18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -1901,7 +1901,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -2620,28 +2620,28 @@
         <v>38</v>
       </c>
       <c r="D16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>30</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>9.09</v>
+        <v>11.76</v>
       </c>
       <c r="I16" s="2">
         <v>7.2</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2690,28 +2690,28 @@
         <v>38</v>
       </c>
       <c r="D18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18">
         <v>25</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>10.71</v>
+        <v>13.79</v>
       </c>
       <c r="I18" s="2">
         <v>7.7</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="19" spans="1:11">

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="40">
   <si>
     <t>Docente</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Por_Blan</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Avila Coronado Julieta</t>
   </si>
   <si>
     <t>González Nuñez Veronica</t>
@@ -60,9 +60,57 @@
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>4AEM</t>
+  </si>
+  <si>
+    <t>4ALCM</t>
+  </si>
+  <si>
+    <t>4APM</t>
+  </si>
+  <si>
+    <t>4ARHM</t>
+  </si>
+  <si>
+    <t>4BEM</t>
+  </si>
+  <si>
+    <t>4BLCM</t>
+  </si>
+  <si>
+    <t>2APV</t>
+  </si>
+  <si>
+    <t>4AEV</t>
+  </si>
+  <si>
+    <t>4ALCV</t>
+  </si>
+  <si>
+    <t>4APV</t>
+  </si>
+  <si>
+    <t>4ARHV</t>
+  </si>
+  <si>
+    <t>4ASV</t>
+  </si>
+  <si>
+    <t>2ALCV</t>
+  </si>
+  <si>
+    <t>2ARHV</t>
+  </si>
+  <si>
+    <t>2ASV</t>
+  </si>
+  <si>
     <t>2AEM</t>
   </si>
   <si>
@@ -81,58 +129,13 @@
     <t>2BLCM</t>
   </si>
   <si>
-    <t>4AEM</t>
-  </si>
-  <si>
-    <t>4ALCM</t>
-  </si>
-  <si>
-    <t>4APM</t>
-  </si>
-  <si>
-    <t>4ARHM</t>
-  </si>
-  <si>
-    <t>4BEM</t>
-  </si>
-  <si>
-    <t>4BLCM</t>
-  </si>
-  <si>
-    <t>2APV</t>
-  </si>
-  <si>
-    <t>4AEV</t>
-  </si>
-  <si>
-    <t>4ALCV</t>
-  </si>
-  <si>
-    <t>4APV</t>
-  </si>
-  <si>
-    <t>4ARHV</t>
-  </si>
-  <si>
-    <t>4ASV</t>
-  </si>
-  <si>
-    <t>2ALCV</t>
-  </si>
-  <si>
-    <t>2ARHV</t>
-  </si>
-  <si>
-    <t>2ASV</t>
-  </si>
-  <si>
     <t>2AEV</t>
   </si>
   <si>
+    <t>INGLÉS IV</t>
+  </si>
+  <si>
     <t>INGLÉS II</t>
-  </si>
-  <si>
-    <t>INGLÉS IV</t>
   </si>
 </sst>
 </file>
@@ -546,28 +549,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>94.12</v>
+        <v>61.29</v>
       </c>
       <c r="H2" s="1">
-        <v>5.88</v>
+        <v>38.71</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -581,28 +584,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>97.67</v>
+        <v>78.05</v>
       </c>
       <c r="H3" s="1">
-        <v>2.33</v>
+        <v>21.95</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -616,28 +619,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -651,28 +654,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>95</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>5</v>
+        <v>26.32</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -686,28 +689,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>91.89</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>8.109999999999999</v>
+        <v>21.43</v>
       </c>
       <c r="I6" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -721,28 +724,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>41</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
-        <v>92.68000000000001</v>
+        <v>63.41</v>
       </c>
       <c r="H7" s="1">
-        <v>7.32</v>
+        <v>36.59</v>
       </c>
       <c r="I7" s="2">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -753,31 +756,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>61.29</v>
+        <v>93.33</v>
       </c>
       <c r="H8" s="1">
-        <v>38.71</v>
+        <v>6.67</v>
       </c>
       <c r="I8" s="2">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -788,31 +791,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1">
-        <v>78.05</v>
+        <v>61.29</v>
       </c>
       <c r="H9" s="1">
-        <v>21.95</v>
+        <v>38.71</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -823,66 +826,66 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>38</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>85.70999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>14.29</v>
+        <v>11.76</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
       </c>
       <c r="D11">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F11">
         <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>73.68000000000001</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1">
-        <v>26.32</v>
+        <v>40</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -893,66 +896,66 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12">
+        <v>29</v>
+      </c>
+      <c r="E12">
         <v>25</v>
       </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12">
-        <v>28</v>
-      </c>
-      <c r="E12">
-        <v>22</v>
-      </c>
       <c r="F12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>78.56999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>21.43</v>
+        <v>13.79</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>38</v>
       </c>
       <c r="D13">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E13">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>63.41</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>36.59</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -963,31 +966,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>93.33</v>
+        <v>92.86</v>
       </c>
       <c r="H14" s="1">
-        <v>6.67</v>
+        <v>7.14</v>
       </c>
       <c r="I14" s="2">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -998,31 +1001,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15">
+        <v>32</v>
+      </c>
+      <c r="E15">
         <v>31</v>
       </c>
-      <c r="E15">
-        <v>19</v>
-      </c>
       <c r="F15">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>61.29</v>
+        <v>96.88</v>
       </c>
       <c r="H15" s="1">
-        <v>38.71</v>
+        <v>3.13</v>
       </c>
       <c r="I15" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1033,66 +1036,66 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>88.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>11.76</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>60</v>
+        <v>94.12</v>
       </c>
       <c r="H17" s="1">
-        <v>40</v>
+        <v>5.88</v>
       </c>
       <c r="I17" s="2">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1103,66 +1106,66 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>86.20999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="H18" s="1">
-        <v>13.79</v>
+        <v>2.33</v>
       </c>
       <c r="I18" s="2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="I19" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1173,31 +1176,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>92.86</v>
+        <v>95</v>
       </c>
       <c r="H20" s="1">
-        <v>7.14</v>
+        <v>5</v>
       </c>
       <c r="I20" s="2">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1208,31 +1211,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>37</v>
+      </c>
+      <c r="E21">
         <v>34</v>
       </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21">
-        <v>32</v>
-      </c>
-      <c r="E21">
-        <v>31</v>
-      </c>
       <c r="F21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>96.88</v>
+        <v>91.89</v>
       </c>
       <c r="H21" s="1">
-        <v>3.13</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I21" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1243,31 +1246,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E22">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>100</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="I22" s="2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1278,13 +1281,13 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D23">
         <v>30</v>
@@ -1368,19 +1371,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1389,7 +1392,7 @@
         <v>100</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -1400,19 +1403,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1421,7 +1424,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1432,19 +1435,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1453,7 +1456,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -1464,19 +1467,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1485,7 +1488,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1496,19 +1499,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1517,7 +1520,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1528,10 +1531,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -1557,22 +1560,22 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1581,7 +1584,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1589,22 +1592,22 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1613,7 +1616,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1621,22 +1624,22 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>38</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1645,7 +1648,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1653,22 +1656,22 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
       </c>
       <c r="D11">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1677,7 +1680,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1685,22 +1688,22 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1709,7 +1712,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1717,22 +1720,22 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>38</v>
       </c>
       <c r="D13">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1741,7 +1744,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1749,22 +1752,22 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1773,7 +1776,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1781,22 +1784,22 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1805,7 +1808,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -1813,22 +1816,22 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1837,7 +1840,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -1845,22 +1848,22 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1869,7 +1872,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -1877,22 +1880,22 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -1901,7 +1904,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -1909,22 +1912,22 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -1933,7 +1936,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -1941,22 +1944,22 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -1965,7 +1968,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -1973,22 +1976,22 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
         <v>37</v>
       </c>
-      <c r="D21">
-        <v>32</v>
-      </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -1997,7 +2000,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -2005,22 +2008,22 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -2029,7 +2032,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -2037,13 +2040,13 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D23">
         <v>30</v>
@@ -2124,28 +2127,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>94.12</v>
+        <v>61.29</v>
       </c>
       <c r="H2" s="1">
-        <v>5.88</v>
+        <v>38.71</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2159,28 +2162,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>97.67</v>
+        <v>78.05</v>
       </c>
       <c r="H3" s="1">
-        <v>2.33</v>
+        <v>21.95</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2194,28 +2197,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2229,28 +2232,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>95</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>5</v>
+        <v>26.32</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2264,28 +2267,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>91.89</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>8.109999999999999</v>
+        <v>21.43</v>
       </c>
       <c r="I6" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2299,28 +2302,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>41</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
-        <v>92.68000000000001</v>
+        <v>63.41</v>
       </c>
       <c r="H7" s="1">
-        <v>7.32</v>
+        <v>36.59</v>
       </c>
       <c r="I7" s="2">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2331,31 +2334,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>61.29</v>
+        <v>93.33</v>
       </c>
       <c r="H8" s="1">
-        <v>38.71</v>
+        <v>6.67</v>
       </c>
       <c r="I8" s="2">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2366,31 +2369,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1">
-        <v>78.05</v>
+        <v>61.29</v>
       </c>
       <c r="H9" s="1">
-        <v>21.95</v>
+        <v>38.71</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2401,66 +2404,66 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>38</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>85.70999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>14.29</v>
+        <v>11.76</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
       </c>
       <c r="D11">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F11">
         <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>73.68000000000001</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1">
-        <v>26.32</v>
+        <v>40</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2471,66 +2474,66 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12">
+        <v>29</v>
+      </c>
+      <c r="E12">
         <v>25</v>
       </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12">
-        <v>28</v>
-      </c>
-      <c r="E12">
-        <v>22</v>
-      </c>
       <c r="F12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>78.56999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>21.43</v>
+        <v>13.79</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>38</v>
       </c>
       <c r="D13">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E13">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>63.41</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>36.59</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2541,31 +2544,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>93.33</v>
+        <v>92.86</v>
       </c>
       <c r="H14" s="1">
-        <v>6.67</v>
+        <v>7.14</v>
       </c>
       <c r="I14" s="2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2576,31 +2579,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15">
+        <v>32</v>
+      </c>
+      <c r="E15">
         <v>31</v>
       </c>
-      <c r="E15">
-        <v>19</v>
-      </c>
       <c r="F15">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>61.29</v>
+        <v>96.88</v>
       </c>
       <c r="H15" s="1">
-        <v>38.71</v>
+        <v>3.13</v>
       </c>
       <c r="I15" s="2">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2611,66 +2614,66 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>88.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>11.76</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>60</v>
+        <v>94.12</v>
       </c>
       <c r="H17" s="1">
-        <v>40</v>
+        <v>5.88</v>
       </c>
       <c r="I17" s="2">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2681,66 +2684,66 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>86.20999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="H18" s="1">
-        <v>13.79</v>
+        <v>2.33</v>
       </c>
       <c r="I18" s="2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="I19" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2751,31 +2754,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>92.86</v>
+        <v>95</v>
       </c>
       <c r="H20" s="1">
-        <v>7.14</v>
+        <v>5</v>
       </c>
       <c r="I20" s="2">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2786,31 +2789,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>37</v>
+      </c>
+      <c r="E21">
         <v>34</v>
       </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21">
-        <v>32</v>
-      </c>
-      <c r="E21">
-        <v>31</v>
-      </c>
       <c r="F21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>96.88</v>
+        <v>91.89</v>
       </c>
       <c r="H21" s="1">
-        <v>3.13</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I21" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2821,31 +2824,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E22">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>100</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="I22" s="2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2856,13 +2859,13 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D23">
         <v>30</v>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="41">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
@@ -63,9 +62,18 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>INGLÉS IV</t>
+  </si>
+  <si>
+    <t>INGLÉS II</t>
+  </si>
+  <si>
     <t>4AEM</t>
   </si>
   <si>
@@ -130,12 +138,6 @@
   </si>
   <si>
     <t>2AEV</t>
-  </si>
-  <si>
-    <t>INGLÉS IV</t>
-  </si>
-  <si>
-    <t>INGLÉS II</t>
   </si>
 </sst>
 </file>
@@ -499,11 +501,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -549,10 +551,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -564,10 +566,10 @@
         <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>61.29</v>
+        <v>61.3</v>
       </c>
       <c r="H2" s="1">
-        <v>38.71</v>
+        <v>38.7</v>
       </c>
       <c r="I2" s="2">
         <v>6.9</v>
@@ -587,7 +589,7 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -599,10 +601,10 @@
         <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>78.05</v>
+        <v>78</v>
       </c>
       <c r="H3" s="1">
-        <v>21.95</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2">
         <v>7.4</v>
@@ -619,10 +621,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>28</v>
@@ -634,10 +636,10 @@
         <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>85.70999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H4" s="1">
-        <v>14.29</v>
+        <v>14.3</v>
       </c>
       <c r="I4" s="2">
         <v>7.8</v>
@@ -654,10 +656,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>38</v>
@@ -669,10 +671,10 @@
         <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>73.68000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="H5" s="1">
-        <v>26.32</v>
+        <v>26.3</v>
       </c>
       <c r="I5" s="2">
         <v>7.2</v>
@@ -689,10 +691,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -704,10 +706,10 @@
         <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>78.56999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="I6" s="2">
         <v>7.4</v>
@@ -724,10 +726,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -739,10 +741,10 @@
         <v>15</v>
       </c>
       <c r="G7" s="1">
-        <v>63.41</v>
+        <v>63.4</v>
       </c>
       <c r="H7" s="1">
-        <v>36.59</v>
+        <v>36.6</v>
       </c>
       <c r="I7" s="2">
         <v>6.3</v>
@@ -756,31 +758,25 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>207</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>151</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="G8" s="1">
-        <v>93.33</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>6.67</v>
+        <v>27.1</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -794,28 +790,28 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>61.29</v>
+        <v>93.3</v>
       </c>
       <c r="H9" s="1">
-        <v>38.71</v>
+        <v>6.7</v>
       </c>
       <c r="I9" s="2">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -829,34 +825,34 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1">
-        <v>88.23999999999999</v>
+        <v>61.3</v>
       </c>
       <c r="H10" s="1">
-        <v>11.76</v>
+        <v>38.7</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -864,34 +860,34 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D11">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>60</v>
+        <v>88.2</v>
       </c>
       <c r="H11" s="1">
-        <v>40</v>
+        <v>11.8</v>
       </c>
       <c r="I11" s="2">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -899,34 +895,34 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D12">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>86.20999999999999</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1">
-        <v>13.79</v>
+        <v>40</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -934,63 +930,63 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D13">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D14">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="E14">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>92.86</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1001,37 +997,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D15">
+        <v>163</v>
+      </c>
+      <c r="E15">
+        <v>131</v>
+      </c>
+      <c r="F15">
         <v>32</v>
       </c>
-      <c r="E15">
-        <v>31</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
       <c r="G15" s="1">
-        <v>96.88</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>3.13</v>
+        <v>19.6</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1039,28 +1029,28 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E16">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="I16" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1071,31 +1061,31 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17">
         <v>31</v>
       </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17">
-        <v>34</v>
-      </c>
-      <c r="E17">
-        <v>32</v>
-      </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>94.12</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>5.88</v>
+        <v>3.1</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1106,31 +1096,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D18">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E18">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>97.67</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1141,31 +1131,25 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D19">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="E19">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>92.31</v>
+        <v>96.2</v>
       </c>
       <c r="H19" s="1">
-        <v>7.69</v>
+        <v>3.8</v>
       </c>
       <c r="I19" s="2">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1179,28 +1163,28 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
         <v>34</v>
       </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
       <c r="D20">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E20">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>95</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="I20" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1214,28 +1198,28 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
         <v>35</v>
       </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
       <c r="D21">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E21">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>91.89</v>
+        <v>97.7</v>
       </c>
       <c r="H21" s="1">
-        <v>8.109999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="I21" s="2">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1249,28 +1233,28 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
         <v>36</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22">
         <v>39</v>
       </c>
-      <c r="D22">
-        <v>41</v>
-      </c>
       <c r="E22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F22">
         <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>92.68000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H22" s="1">
-        <v>7.32</v>
+        <v>7.7</v>
       </c>
       <c r="I22" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1281,36 +1265,228 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23">
+        <v>40</v>
+      </c>
+      <c r="E23">
+        <v>38</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" s="1">
+        <v>95</v>
+      </c>
+      <c r="H23" s="1">
+        <v>5</v>
+      </c>
+      <c r="I23" s="2">
+        <v>8</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24">
+        <v>37</v>
+      </c>
+      <c r="E24">
+        <v>34</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H24" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25">
+        <v>42</v>
+      </c>
+      <c r="E25">
+        <v>39</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H25" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26">
+        <v>235</v>
+      </c>
+      <c r="E26">
+        <v>221</v>
+      </c>
+      <c r="F26">
+        <v>14</v>
+      </c>
+      <c r="G26" s="1">
+        <v>94</v>
+      </c>
+      <c r="H26" s="1">
+        <v>6</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
         <v>15</v>
       </c>
-      <c r="B23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23">
+      <c r="D27">
+        <v>741</v>
+      </c>
+      <c r="E27">
+        <v>614</v>
+      </c>
+      <c r="F27">
+        <v>127</v>
+      </c>
+      <c r="G27" s="1">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="H27" s="1">
+        <v>17.1</v>
+      </c>
+      <c r="I27" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28">
         <v>30</v>
       </c>
-      <c r="E23">
+      <c r="E28">
         <v>9</v>
       </c>
-      <c r="F23">
+      <c r="F28">
         <v>21</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G28" s="1">
         <v>30</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H28" s="1">
         <v>70</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I28" s="2">
         <v>4.8</v>
       </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29">
+        <v>30</v>
+      </c>
+      <c r="E29">
+        <v>9</v>
+      </c>
+      <c r="F29">
+        <v>21</v>
+      </c>
+      <c r="G29" s="1">
+        <v>30</v>
+      </c>
+      <c r="H29" s="1">
+        <v>70</v>
+      </c>
+      <c r="I29" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1321,11 +1497,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1371,31 +1547,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>38.7</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.9</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1406,28 +1585,31 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>41</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>22</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.4</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1435,31 +1617,34 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>14.3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1467,31 +1652,34 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>38</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>73.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>26.3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.2</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1499,31 +1687,34 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>28</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>21.4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1531,63 +1722,63 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>63.4</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>36.6</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.3</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>207</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>27.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1595,31 +1786,34 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>6.7</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1627,31 +1821,34 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>38.7</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.5</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1659,31 +1856,34 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D11">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>11.8</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.2</v>
       </c>
       <c r="J11">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1691,31 +1891,34 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D12">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.5</v>
       </c>
       <c r="J12">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1723,95 +1926,98 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D13">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>86.2</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>13.8</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.7</v>
       </c>
       <c r="J13">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D14">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.4</v>
       </c>
       <c r="J14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D15">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F15">
         <v>32</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>19.6</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.2</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1819,127 +2025,133 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>7.3</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17">
         <v>31</v>
       </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17">
-        <v>34</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
       <c r="F17">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>3.1</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.3</v>
       </c>
       <c r="J17">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D18">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F18">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D19">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="F19">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>3.8</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.2</v>
       </c>
       <c r="J19">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1947,31 +2159,34 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
         <v>34</v>
       </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
       <c r="D20">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>5.9</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7.8</v>
       </c>
       <c r="J20">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1979,31 +2194,34 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
         <v>35</v>
       </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
       <c r="D21">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F21">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>2.3</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8.6</v>
       </c>
       <c r="J21">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2011,884 +2229,260 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
         <v>36</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22">
         <v>39</v>
       </c>
-      <c r="D22">
-        <v>41</v>
-      </c>
       <c r="E22">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F22">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>7.7</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.7</v>
       </c>
       <c r="J22">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23">
+        <v>40</v>
+      </c>
+      <c r="E23">
+        <v>38</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" s="1">
+        <v>95</v>
+      </c>
+      <c r="H23" s="1">
+        <v>5</v>
+      </c>
+      <c r="I23" s="2">
+        <v>8</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24">
+        <v>37</v>
+      </c>
+      <c r="E24">
+        <v>34</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H24" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25">
+        <v>42</v>
+      </c>
+      <c r="E25">
+        <v>39</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H25" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26">
+        <v>235</v>
+      </c>
+      <c r="E26">
+        <v>221</v>
+      </c>
+      <c r="F26">
+        <v>14</v>
+      </c>
+      <c r="G26" s="1">
+        <v>94</v>
+      </c>
+      <c r="H26" s="1">
+        <v>6</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
         <v>15</v>
       </c>
-      <c r="B23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23">
+      <c r="D27">
+        <v>741</v>
+      </c>
+      <c r="E27">
+        <v>614</v>
+      </c>
+      <c r="F27">
+        <v>127</v>
+      </c>
+      <c r="G27" s="1">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="H27" s="1">
+        <v>17.1</v>
+      </c>
+      <c r="I27" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28">
         <v>30</v>
       </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
+      <c r="E28">
+        <v>9</v>
+      </c>
+      <c r="F28">
+        <v>21</v>
+      </c>
+      <c r="G28" s="1">
         <v>30</v>
       </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>100</v>
-      </c>
-      <c r="J23">
+      <c r="H28" s="1">
+        <v>70</v>
+      </c>
+      <c r="I28" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29">
         <v>30</v>
       </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="E29">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2">
-        <v>31</v>
-      </c>
-      <c r="E2">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1">
-        <v>61.29</v>
-      </c>
-      <c r="H2" s="1">
-        <v>38.71</v>
-      </c>
-      <c r="I2" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3">
-        <v>41</v>
-      </c>
-      <c r="E3">
-        <v>32</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3" s="1">
-        <v>78.05</v>
-      </c>
-      <c r="H3" s="1">
-        <v>21.95</v>
-      </c>
-      <c r="I3" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4">
-        <v>28</v>
-      </c>
-      <c r="E4">
-        <v>24</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4" s="1">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="H4" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="I4" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5">
-        <v>38</v>
-      </c>
-      <c r="E5">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5" s="1">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="H5" s="1">
-        <v>26.32</v>
-      </c>
-      <c r="I5" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6">
-        <v>28</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6" s="1">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="H6" s="1">
-        <v>21.43</v>
-      </c>
-      <c r="I6" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="F29">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7">
-        <v>41</v>
-      </c>
-      <c r="E7">
-        <v>26</v>
-      </c>
-      <c r="F7">
-        <v>15</v>
-      </c>
-      <c r="G7" s="1">
-        <v>63.41</v>
-      </c>
-      <c r="H7" s="1">
-        <v>36.59</v>
-      </c>
-      <c r="I7" s="2">
-        <v>6.3</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8">
+      <c r="G29" s="1">
         <v>30</v>
       </c>
-      <c r="E8">
-        <v>28</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>93.33</v>
-      </c>
-      <c r="H8" s="1">
-        <v>6.67</v>
-      </c>
-      <c r="I8" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>19</v>
-      </c>
-      <c r="F9">
-        <v>12</v>
-      </c>
-      <c r="G9" s="1">
-        <v>61.29</v>
-      </c>
-      <c r="H9" s="1">
-        <v>38.71</v>
-      </c>
-      <c r="I9" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10">
-        <v>34</v>
-      </c>
-      <c r="E10">
-        <v>30</v>
-      </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1">
-        <v>88.23999999999999</v>
-      </c>
-      <c r="H10" s="1">
-        <v>11.76</v>
-      </c>
-      <c r="I10" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11">
-        <v>25</v>
-      </c>
-      <c r="E11">
-        <v>15</v>
-      </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1">
-        <v>60</v>
-      </c>
-      <c r="H11" s="1">
-        <v>40</v>
-      </c>
-      <c r="I11" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12">
-        <v>29</v>
-      </c>
-      <c r="E12">
-        <v>25</v>
-      </c>
-      <c r="F12">
-        <v>4</v>
-      </c>
-      <c r="G12" s="1">
-        <v>86.20999999999999</v>
-      </c>
-      <c r="H12" s="1">
-        <v>13.79</v>
-      </c>
-      <c r="I12" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13">
-        <v>14</v>
-      </c>
-      <c r="E13">
-        <v>14</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>100</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14">
-        <v>42</v>
-      </c>
-      <c r="E14">
-        <v>39</v>
-      </c>
-      <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="G14" s="1">
-        <v>92.86</v>
-      </c>
-      <c r="H14" s="1">
-        <v>7.14</v>
-      </c>
-      <c r="I14" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15">
-        <v>32</v>
-      </c>
-      <c r="E15">
-        <v>31</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>96.88</v>
-      </c>
-      <c r="H15" s="1">
-        <v>3.13</v>
-      </c>
-      <c r="I15" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16">
-        <v>33</v>
-      </c>
-      <c r="E16">
-        <v>33</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>100</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17">
-        <v>34</v>
-      </c>
-      <c r="E17">
-        <v>32</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17" s="1">
-        <v>94.12</v>
-      </c>
-      <c r="H17" s="1">
-        <v>5.88</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18">
-        <v>43</v>
-      </c>
-      <c r="E18">
-        <v>42</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>97.67</v>
-      </c>
-      <c r="H18" s="1">
-        <v>2.33</v>
-      </c>
-      <c r="I18" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19">
-        <v>39</v>
-      </c>
-      <c r="E19">
-        <v>36</v>
-      </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="G19" s="1">
-        <v>92.31</v>
-      </c>
-      <c r="H19" s="1">
-        <v>7.69</v>
-      </c>
-      <c r="I19" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20">
-        <v>40</v>
-      </c>
-      <c r="E20">
-        <v>38</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-      <c r="G20" s="1">
-        <v>95</v>
-      </c>
-      <c r="H20" s="1">
-        <v>5</v>
-      </c>
-      <c r="I20" s="2">
-        <v>8</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21">
-        <v>37</v>
-      </c>
-      <c r="E21">
-        <v>34</v>
-      </c>
-      <c r="F21">
-        <v>3</v>
-      </c>
-      <c r="G21" s="1">
-        <v>91.89</v>
-      </c>
-      <c r="H21" s="1">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="I21" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22">
-        <v>41</v>
-      </c>
-      <c r="E22">
-        <v>38</v>
-      </c>
-      <c r="F22">
-        <v>3</v>
-      </c>
-      <c r="G22" s="1">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="H22" s="1">
-        <v>7.32</v>
-      </c>
-      <c r="I22" s="2">
-        <v>8</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23">
-        <v>30</v>
-      </c>
-      <c r="E23">
-        <v>9</v>
-      </c>
-      <c r="F23">
-        <v>21</v>
-      </c>
-      <c r="G23" s="1">
-        <v>30</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="H29" s="1">
         <v>70</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I29" s="2">
         <v>5.5</v>
       </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="42">
   <si>
     <t>Docente</t>
   </si>
@@ -62,16 +62,19 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
     <t>INGLÉS IV</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>INGLÉS II</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>4AEM</t>
@@ -505,7 +508,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -551,10 +554,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -586,10 +589,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -621,10 +624,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>28</v>
@@ -656,10 +659,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>38</v>
@@ -691,10 +694,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -726,10 +729,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -760,6 +763,9 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
       <c r="D8">
         <v>207</v>
       </c>
@@ -793,7 +799,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>30</v>
@@ -825,10 +831,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>31</v>
@@ -860,10 +866,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>34</v>
@@ -895,10 +901,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>25</v>
@@ -930,10 +936,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>29</v>
@@ -965,10 +971,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>14</v>
@@ -999,6 +1005,9 @@
       <c r="A15" t="s">
         <v>12</v>
       </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
       <c r="D15">
         <v>163</v>
       </c>
@@ -1032,7 +1041,7 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>41</v>
@@ -1067,7 +1076,7 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>32</v>
@@ -1102,7 +1111,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>33</v>
@@ -1133,6 +1142,9 @@
       <c r="A19" t="s">
         <v>13</v>
       </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
       <c r="D19">
         <v>106</v>
       </c>
@@ -1166,7 +1178,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20">
         <v>34</v>
@@ -1201,7 +1213,7 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21">
         <v>43</v>
@@ -1236,7 +1248,7 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22">
         <v>39</v>
@@ -1271,7 +1283,7 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23">
         <v>40</v>
@@ -1306,7 +1318,7 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24">
         <v>37</v>
@@ -1341,7 +1353,7 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25">
         <v>42</v>
@@ -1372,6 +1384,9 @@
       <c r="A26" t="s">
         <v>14</v>
       </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
       <c r="D26">
         <v>235</v>
       </c>
@@ -1401,40 +1416,43 @@
       <c r="A27" t="s">
         <v>15</v>
       </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
       <c r="D27">
-        <v>741</v>
+        <v>30</v>
       </c>
       <c r="E27">
-        <v>614</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="G27" s="1">
-        <v>82.90000000000001</v>
+        <v>30</v>
       </c>
       <c r="H27" s="1">
-        <v>17.1</v>
+        <v>70</v>
       </c>
       <c r="I27" s="2">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D28">
         <v>30</v>
@@ -1462,32 +1480,32 @@
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>16</v>
+      <c r="B29" t="s">
+        <v>19</v>
       </c>
       <c r="D29">
-        <v>30</v>
+        <v>741</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>614</v>
       </c>
       <c r="F29">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="G29" s="1">
-        <v>30</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H29" s="1">
-        <v>70</v>
+        <v>17.1</v>
       </c>
       <c r="I29" s="2">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1547,10 +1565,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -1582,10 +1600,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -1617,10 +1635,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>28</v>
@@ -1652,10 +1670,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>38</v>
@@ -1687,10 +1705,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -1722,10 +1740,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -1756,6 +1774,9 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
       <c r="D8">
         <v>207</v>
       </c>
@@ -1789,7 +1810,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>30</v>
@@ -1821,10 +1842,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>31</v>
@@ -1856,10 +1877,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>34</v>
@@ -1891,10 +1912,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>25</v>
@@ -1926,10 +1947,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>29</v>
@@ -1961,10 +1982,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>14</v>
@@ -1995,6 +2016,9 @@
       <c r="A15" t="s">
         <v>12</v>
       </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
       <c r="D15">
         <v>163</v>
       </c>
@@ -2028,7 +2052,7 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>41</v>
@@ -2063,7 +2087,7 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>32</v>
@@ -2098,7 +2122,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>33</v>
@@ -2129,6 +2153,9 @@
       <c r="A19" t="s">
         <v>13</v>
       </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
       <c r="D19">
         <v>106</v>
       </c>
@@ -2162,7 +2189,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20">
         <v>34</v>
@@ -2197,7 +2224,7 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21">
         <v>43</v>
@@ -2232,7 +2259,7 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22">
         <v>39</v>
@@ -2267,7 +2294,7 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23">
         <v>40</v>
@@ -2302,7 +2329,7 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24">
         <v>37</v>
@@ -2337,7 +2364,7 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25">
         <v>42</v>
@@ -2368,6 +2395,9 @@
       <c r="A26" t="s">
         <v>14</v>
       </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
       <c r="D26">
         <v>235</v>
       </c>
@@ -2397,40 +2427,43 @@
       <c r="A27" t="s">
         <v>15</v>
       </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
       <c r="D27">
-        <v>741</v>
+        <v>30</v>
       </c>
       <c r="E27">
-        <v>614</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="G27" s="1">
-        <v>82.90000000000001</v>
+        <v>30</v>
       </c>
       <c r="H27" s="1">
-        <v>17.1</v>
+        <v>70</v>
       </c>
       <c r="I27" s="2">
-        <v>7.3</v>
+        <v>5.5</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D28">
         <v>30</v>
@@ -2458,32 +2491,32 @@
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>16</v>
+      <c r="B29" t="s">
+        <v>19</v>
       </c>
       <c r="D29">
-        <v>30</v>
+        <v>741</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>614</v>
       </c>
       <c r="F29">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="G29" s="1">
-        <v>30</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H29" s="1">
-        <v>70</v>
+        <v>17.1</v>
       </c>
       <c r="I29" s="2">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="42">
   <si>
     <t>Docente</t>
   </si>
@@ -1574,6 +1575,1017 @@
         <v>31</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>31</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>41</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>41</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>28</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>38</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>38</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>38</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>28</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>41</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>41</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>207</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>207</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>207</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10">
+        <v>31</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>31</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>31</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11">
+        <v>34</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>34</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>25</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>25</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>25</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>29</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>29</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>14</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>14</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15">
+        <v>163</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>163</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>163</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16">
+        <v>41</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>41</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>41</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>32</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>32</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18">
+        <v>33</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>33</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>33</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>106</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>106</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>106</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20">
+        <v>34</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>34</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>34</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21">
+        <v>43</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>43</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>43</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22">
+        <v>39</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>39</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>100</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>39</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23">
+        <v>40</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>40</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>40</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>37</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>37</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>100</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>37</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25">
+        <v>42</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>42</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>100</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>42</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26">
+        <v>235</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>235</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>100</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>235</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27">
+        <v>30</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>30</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>100</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>30</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28">
+        <v>30</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>30</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>100</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>30</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29">
+        <v>741</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>741</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>100</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>741</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>31</v>
+      </c>
+      <c r="E2">
         <v>19</v>
       </c>
       <c r="F2">

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -1080,28 +1080,28 @@
         <v>33</v>
       </c>
       <c r="D17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>31</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>96.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>3.1</v>
+        <v>6.1</v>
       </c>
       <c r="I17" s="2">
         <v>7.3</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1147,28 +1147,28 @@
         <v>17</v>
       </c>
       <c r="D19">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19">
         <v>102</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>96.2</v>
+        <v>95.3</v>
       </c>
       <c r="H19" s="1">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="I19" s="2">
         <v>7.2</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1485,28 +1485,28 @@
         <v>19</v>
       </c>
       <c r="D29">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E29">
         <v>614</v>
       </c>
       <c r="F29">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G29" s="1">
-        <v>82.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="H29" s="1">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="I29" s="2">
         <v>7.3</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="1">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -1575,25 +1575,25 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>22.6</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1610,25 +1610,25 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>17.1</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1645,25 +1645,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1680,25 +1680,25 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1715,25 +1715,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1750,25 +1750,25 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>63.4</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>36.6</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1782,25 +1782,25 @@
         <v>207</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="F8">
-        <v>207</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>76.8</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>23.2</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2091,13 +2091,13 @@
         <v>33</v>
       </c>
       <c r="D17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -2129,25 +2129,25 @@
         <v>33</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F18">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2158,28 +2158,28 @@
         <v>17</v>
       </c>
       <c r="D19">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>69.2</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J19">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2496,28 +2496,28 @@
         <v>19</v>
       </c>
       <c r="D29">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="F29">
-        <v>741</v>
+        <v>550</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J29">
-        <v>741</v>
+        <v>502</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>67.7</v>
       </c>
     </row>
   </sheetData>
@@ -2586,19 +2586,19 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>61.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>38.7</v>
+        <v>22.6</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2621,19 +2621,19 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>78</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>22</v>
+        <v>17.1</v>
       </c>
       <c r="I3" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>14.3</v>
       </c>
       <c r="I4" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2691,19 +2691,19 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>73.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>26.3</v>
+        <v>21.1</v>
       </c>
       <c r="I5" s="2">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2726,19 +2726,19 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>78.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="H6" s="1">
-        <v>21.4</v>
+        <v>25</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2773,7 +2773,7 @@
         <v>36.6</v>
       </c>
       <c r="I7" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2793,19 +2793,19 @@
         <v>207</v>
       </c>
       <c r="E8">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F8">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1">
-        <v>72.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="H8" s="1">
-        <v>27.1</v>
+        <v>23.2</v>
       </c>
       <c r="I8" s="2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3102,28 +3102,28 @@
         <v>33</v>
       </c>
       <c r="D17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>31</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>96.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>3.1</v>
+        <v>6.1</v>
       </c>
       <c r="I17" s="2">
         <v>7.3</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3169,28 +3169,28 @@
         <v>17</v>
       </c>
       <c r="D19">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19">
         <v>102</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>96.2</v>
+        <v>95.3</v>
       </c>
       <c r="H19" s="1">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="I19" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3507,28 +3507,28 @@
         <v>19</v>
       </c>
       <c r="D29">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E29">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="F29">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G29" s="1">
-        <v>82.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="H29" s="1">
-        <v>17.1</v>
+        <v>16.2</v>
       </c>
       <c r="I29" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="1">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -1083,25 +1083,25 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="H17" s="1">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="I17" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1150,25 +1150,25 @@
         <v>107</v>
       </c>
       <c r="E19">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>95.3</v>
+        <v>96.3</v>
       </c>
       <c r="H19" s="1">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="I19" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1488,25 +1488,25 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F29">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G29" s="1">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H29" s="1">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="I29" s="2">
         <v>7.3</v>
       </c>
       <c r="J29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -2094,25 +2094,25 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2161,25 +2161,25 @@
         <v>107</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F19">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="G19" s="1">
-        <v>30.8</v>
+        <v>60.7</v>
       </c>
       <c r="H19" s="1">
-        <v>69.2</v>
+        <v>39.3</v>
       </c>
       <c r="I19" s="2">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J19">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="K19" s="1">
-        <v>69.2</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2196,25 +2196,25 @@
         <v>34</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J20">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2231,25 +2231,25 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F21">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>95.3</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>4.7</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2266,25 +2266,25 @@
         <v>39</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F22">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>15.4</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2301,25 +2301,25 @@
         <v>40</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J23">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2336,25 +2336,25 @@
         <v>37</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F24">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>13.5</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J24">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2371,25 +2371,25 @@
         <v>42</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F25">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J25">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2403,25 +2403,25 @@
         <v>235</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="F26">
-        <v>235</v>
+        <v>29</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>87.7</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>12.3</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J26">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2499,25 +2499,25 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>192</v>
+        <v>430</v>
       </c>
       <c r="F29">
-        <v>550</v>
+        <v>312</v>
       </c>
       <c r="G29" s="1">
-        <v>25.9</v>
+        <v>58</v>
       </c>
       <c r="H29" s="1">
-        <v>74.09999999999999</v>
+        <v>42</v>
       </c>
       <c r="I29" s="2">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>502</v>
+        <v>235</v>
       </c>
       <c r="K29" s="1">
-        <v>67.7</v>
+        <v>31.7</v>
       </c>
     </row>
   </sheetData>
@@ -3105,25 +3105,25 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3172,25 +3172,25 @@
         <v>107</v>
       </c>
       <c r="E19">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>95.3</v>
+        <v>97.2</v>
       </c>
       <c r="H19" s="1">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="I19" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3207,19 +3207,19 @@
         <v>34</v>
       </c>
       <c r="E20">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>94.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="H20" s="1">
-        <v>5.9</v>
+        <v>14.7</v>
       </c>
       <c r="I20" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3242,19 +3242,19 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="H21" s="1">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="I21" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3277,19 +3277,19 @@
         <v>39</v>
       </c>
       <c r="E22">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1">
-        <v>92.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="I22" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3312,19 +3312,19 @@
         <v>40</v>
       </c>
       <c r="E23">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="H23" s="1">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3347,19 +3347,19 @@
         <v>37</v>
       </c>
       <c r="E24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1">
-        <v>91.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="H24" s="1">
-        <v>8.1</v>
+        <v>13.5</v>
       </c>
       <c r="I24" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3382,16 +3382,16 @@
         <v>42</v>
       </c>
       <c r="E25">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1">
-        <v>92.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H25" s="1">
-        <v>7.1</v>
+        <v>14.3</v>
       </c>
       <c r="I25" s="2">
         <v>8.1</v>
@@ -3414,19 +3414,19 @@
         <v>235</v>
       </c>
       <c r="E26">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="F26">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G26" s="1">
-        <v>94</v>
+        <v>87.7</v>
       </c>
       <c r="H26" s="1">
-        <v>6</v>
+        <v>12.3</v>
       </c>
       <c r="I26" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3510,25 +3510,25 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="F29">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="G29" s="1">
-        <v>83.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>16.2</v>
+        <v>17.9</v>
       </c>
       <c r="I29" s="2">
         <v>7.5</v>
       </c>
       <c r="J29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -2438,25 +2438,25 @@
         <v>30</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J27">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2470,25 +2470,25 @@
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J28">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2499,25 +2499,25 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="F29">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G29" s="1">
-        <v>58</v>
+        <v>59.3</v>
       </c>
       <c r="H29" s="1">
-        <v>42</v>
+        <v>40.7</v>
       </c>
       <c r="I29" s="2">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J29">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="K29" s="1">
-        <v>31.7</v>
+        <v>27.6</v>
       </c>
     </row>
   </sheetData>
@@ -3449,19 +3449,19 @@
         <v>30</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" s="1">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="H27" s="1">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="I27" s="2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3481,19 +3481,19 @@
         <v>30</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G28" s="1">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="H28" s="1">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="I28" s="2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F29">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G29" s="1">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="H29" s="1">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="I29" s="2">
         <v>7.5</v>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -1817,25 +1817,25 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>13.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1852,25 +1852,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>58.1</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>41.9</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1887,25 +1887,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1922,25 +1922,25 @@
         <v>25</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F12">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J12">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1957,25 +1957,25 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>17.2</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1992,25 +1992,25 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2024,25 +2024,25 @@
         <v>163</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="F15">
-        <v>163</v>
+        <v>39</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>23.9</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
-        <v>163</v>
+        <v>15</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2059,25 +2059,25 @@
         <v>41</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F16">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>7.3</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J16">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2094,25 +2094,25 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
         <v>7.9</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2161,25 +2161,25 @@
         <v>107</v>
       </c>
       <c r="E19">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="F19">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>60.7</v>
+        <v>97.2</v>
       </c>
       <c r="H19" s="1">
-        <v>39.3</v>
+        <v>2.8</v>
       </c>
       <c r="I19" s="2">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>39.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2499,25 +2499,25 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>440</v>
+        <v>603</v>
       </c>
       <c r="F29">
-        <v>302</v>
+        <v>139</v>
       </c>
       <c r="G29" s="1">
-        <v>59.3</v>
+        <v>81.3</v>
       </c>
       <c r="H29" s="1">
-        <v>40.7</v>
+        <v>18.7</v>
       </c>
       <c r="I29" s="2">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="J29">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="K29" s="1">
-        <v>27.6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2828,19 +2828,19 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="H9" s="1">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2863,19 +2863,19 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>61.3</v>
+        <v>58.1</v>
       </c>
       <c r="H10" s="1">
-        <v>38.7</v>
+        <v>41.9</v>
       </c>
       <c r="I10" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2898,19 +2898,19 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2945,7 +2945,7 @@
         <v>40</v>
       </c>
       <c r="I12" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2968,19 +2968,19 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>86.2</v>
+        <v>82.8</v>
       </c>
       <c r="H13" s="1">
-        <v>13.8</v>
+        <v>17.2</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -3003,19 +3003,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>163</v>
       </c>
       <c r="E15">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G15" s="1">
-        <v>80.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="H15" s="1">
-        <v>19.6</v>
+        <v>21.5</v>
       </c>
       <c r="I15" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -3082,7 +3082,7 @@
         <v>7.3</v>
       </c>
       <c r="I16" s="2">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3184,7 +3184,7 @@
         <v>2.8</v>
       </c>
       <c r="I19" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3510,19 +3510,19 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F29">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G29" s="1">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
       <c r="H29" s="1">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="I29" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J29">
         <v>2</v>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -876,25 +876,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="H11" s="1">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" s="2">
         <v>7.3</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -946,25 +946,25 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="H13" s="1">
-        <v>13.8</v>
+        <v>10.3</v>
       </c>
       <c r="I13" s="2">
         <v>7.7</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1013,25 +1013,25 @@
         <v>163</v>
       </c>
       <c r="E15">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G15" s="1">
-        <v>80.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>19.6</v>
+        <v>18.4</v>
       </c>
       <c r="I15" s="2">
         <v>7.2</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1488,25 +1488,25 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="F29">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G29" s="1">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="H29" s="1">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="I29" s="2">
         <v>7.3</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1887,25 +1887,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="I11" s="2">
         <v>7.6</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1922,25 +1922,25 @@
         <v>25</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G12" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H12" s="1">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1957,25 +1957,25 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="H13" s="1">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="I13" s="2">
         <v>8</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2024,25 +2024,25 @@
         <v>163</v>
       </c>
       <c r="E15">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F15">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G15" s="1">
-        <v>76.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="H15" s="1">
-        <v>23.9</v>
+        <v>21.5</v>
       </c>
       <c r="I15" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2499,25 +2499,25 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="F29">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G29" s="1">
-        <v>81.3</v>
+        <v>81.8</v>
       </c>
       <c r="H29" s="1">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="I29" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J29">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2898,25 +2898,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="I11" s="2">
         <v>7.5</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2933,19 +2933,19 @@
         <v>25</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G12" s="1">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H12" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2968,25 +2968,25 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="H13" s="1">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="I13" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3050,10 +3050,10 @@
         <v>7.3</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3525,10 +3525,10 @@
         <v>7.6</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -1519,8 +1519,7 @@
   <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2530,8 +2529,7 @@
   <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -3207,19 +3205,19 @@
         <v>34</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>85.3</v>
+        <v>91.2</v>
       </c>
       <c r="H20" s="1">
-        <v>14.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3254,7 +3252,7 @@
         <v>4.7</v>
       </c>
       <c r="I21" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3277,19 +3275,19 @@
         <v>39</v>
       </c>
       <c r="E22">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G22" s="1">
-        <v>84.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>15.4</v>
+        <v>17.9</v>
       </c>
       <c r="I22" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3312,19 +3310,19 @@
         <v>40</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="H23" s="1">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="I23" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3347,19 +3345,19 @@
         <v>37</v>
       </c>
       <c r="E24">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" s="1">
-        <v>86.5</v>
+        <v>83.8</v>
       </c>
       <c r="H24" s="1">
-        <v>13.5</v>
+        <v>16.2</v>
       </c>
       <c r="I24" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3394,7 +3392,7 @@
         <v>14.3</v>
       </c>
       <c r="I25" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3414,19 +3412,19 @@
         <v>235</v>
       </c>
       <c r="E26">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F26">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G26" s="1">
-        <v>87.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="I26" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3510,19 +3508,19 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F29">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G29" s="1">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H29" s="1">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="I29" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J29">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -2689,16 +2689,16 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>78.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="H5" s="1">
-        <v>21.1</v>
+        <v>13.2</v>
       </c>
       <c r="I5" s="2">
         <v>7.7</v>
@@ -2791,16 +2791,16 @@
         <v>207</v>
       </c>
       <c r="E8">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F8">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G8" s="1">
-        <v>76.8</v>
+        <v>78.3</v>
       </c>
       <c r="H8" s="1">
-        <v>23.2</v>
+        <v>21.7</v>
       </c>
       <c r="I8" s="2">
         <v>7.6</v>
@@ -2826,19 +2826,19 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="H9" s="1">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2861,19 +2861,19 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>58.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>41.9</v>
+        <v>19.4</v>
       </c>
       <c r="I10" s="2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         <v>2.9</v>
       </c>
       <c r="I11" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2931,19 +2931,19 @@
         <v>25</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H12" s="1">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I12" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2966,19 +2966,19 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G13" s="1">
-        <v>86.2</v>
+        <v>55.2</v>
       </c>
       <c r="H13" s="1">
-        <v>13.8</v>
+        <v>44.8</v>
       </c>
       <c r="I13" s="2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3001,19 +3001,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>92.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H14" s="1">
-        <v>7.1</v>
+        <v>14.3</v>
       </c>
       <c r="I14" s="2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>163</v>
       </c>
       <c r="E15">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" s="1">
-        <v>78.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         <v>7.3</v>
       </c>
       <c r="I16" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>2.8</v>
       </c>
       <c r="I19" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3508,19 +3508,19 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="F29">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G29" s="1">
-        <v>81.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="H29" s="1">
-        <v>18.1</v>
+        <v>17.5</v>
       </c>
       <c r="I29" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J29">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -2584,19 +2584,19 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>77.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>22.6</v>
+        <v>12.9</v>
       </c>
       <c r="I2" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2619,19 +2619,19 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>82.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="H3" s="1">
-        <v>17.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="H4" s="1">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="I4" s="2">
         <v>8</v>
@@ -2689,16 +2689,16 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>86.8</v>
+        <v>84.2</v>
       </c>
       <c r="H5" s="1">
-        <v>13.2</v>
+        <v>15.8</v>
       </c>
       <c r="I5" s="2">
         <v>7.7</v>
@@ -2724,19 +2724,19 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>75</v>
+        <v>85.7</v>
       </c>
       <c r="H6" s="1">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2759,19 +2759,19 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>63.4</v>
+        <v>78</v>
       </c>
       <c r="H7" s="1">
-        <v>36.6</v>
+        <v>22</v>
       </c>
       <c r="I7" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2791,16 +2791,16 @@
         <v>207</v>
       </c>
       <c r="E8">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="F8">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
-        <v>78.3</v>
+        <v>85.5</v>
       </c>
       <c r="H8" s="1">
-        <v>21.7</v>
+        <v>14.5</v>
       </c>
       <c r="I8" s="2">
         <v>7.6</v>
@@ -3068,16 +3068,16 @@
         <v>41</v>
       </c>
       <c r="E16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>92.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="I16" s="2">
         <v>7.6</v>
@@ -3170,16 +3170,16 @@
         <v>107</v>
       </c>
       <c r="E19">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>97.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="I19" s="2">
         <v>7.7</v>
@@ -3508,16 +3508,16 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="F29">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="G29" s="1">
-        <v>82.5</v>
+        <v>84.8</v>
       </c>
       <c r="H29" s="1">
-        <v>17.5</v>
+        <v>15.2</v>
       </c>
       <c r="I29" s="2">
         <v>7.4</v>

--- a/academias/Inglés - Estadisticos 20222.xlsx
+++ b/academias/Inglés - Estadisticos 20222.xlsx
@@ -3447,19 +3447,19 @@
         <v>30</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G27" s="1">
-        <v>33.3</v>
+        <v>83.3</v>
       </c>
       <c r="H27" s="1">
-        <v>66.7</v>
+        <v>16.7</v>
       </c>
       <c r="I27" s="2">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3479,19 +3479,19 @@
         <v>30</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
-        <v>33.3</v>
+        <v>83.3</v>
       </c>
       <c r="H28" s="1">
-        <v>66.7</v>
+        <v>16.7</v>
       </c>
       <c r="I28" s="2">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3508,16 +3508,16 @@
         <v>742</v>
       </c>
       <c r="E29">
-        <v>629</v>
+        <v>644</v>
       </c>
       <c r="F29">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="G29" s="1">
-        <v>84.8</v>
+        <v>86.8</v>
       </c>
       <c r="H29" s="1">
-        <v>15.2</v>
+        <v>13.2</v>
       </c>
       <c r="I29" s="2">
         <v>7.4</v>
